--- a/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16840" activeTab="8"/>
+    <workbookView windowHeight="16840"/>
   </bookViews>
   <sheets>
     <sheet name="首页" sheetId="15" r:id="rId1"/>
@@ -44,13 +44,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="1026">
   <si>
     <r>
-      <rPr>
-        <sz val="48"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">虹彩炼金3-战痕
 </t>
     </r>
@@ -64,7 +57,7 @@
       </rPr>
       <t xml:space="preserve">
 作者：整洁的魔理沙
-文档版本：V2.4.25.520
+文档版本：V2.4.25.542
 七日杀游戏版本：V2.4</t>
     </r>
   </si>

--- a/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16840"/>
+    <workbookView windowHeight="16840" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="首页" sheetId="15" r:id="rId1"/>
@@ -44,6 +44,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3389" uniqueCount="1026">
   <si>
     <r>
+      <rPr>
+        <sz val="48"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">虹彩炼金3-战痕
 </t>
     </r>
@@ -3473,15 +3480,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFF09457"/>
+      <sz val="24"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="24"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FFF09457"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -7087,10 +7094,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="69" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>487</v>
+        <v>339</v>
       </c>
       <c r="D4" s="69" t="s">
         <v>642</v>
@@ -7685,7 +7692,7 @@
         <v>681</v>
       </c>
       <c r="D18" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="80" t="s">
         <v>682</v>
@@ -7700,7 +7707,7 @@
         <v>666</v>
       </c>
       <c r="I18" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="80" t="s">
         <v>683</v>
@@ -7715,7 +7722,7 @@
         <v>666</v>
       </c>
       <c r="N18" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O18" s="80" t="s">
         <v>669</v>
@@ -7730,7 +7737,7 @@
         <v>666</v>
       </c>
       <c r="S18" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T18" s="80" t="s">
         <v>684</v>
@@ -7758,7 +7765,7 @@
         <v>686</v>
       </c>
       <c r="D19" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="79" t="s">
         <v>687</v>
@@ -7773,7 +7780,7 @@
         <v>666</v>
       </c>
       <c r="I19" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J19" s="79" t="s">
         <v>688</v>
@@ -7788,7 +7795,7 @@
         <v>1</v>
       </c>
       <c r="N19" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O19" s="79" t="s">
         <v>688</v>
@@ -7803,7 +7810,7 @@
         <v>666</v>
       </c>
       <c r="S19" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T19" s="65" t="s">
         <v>689</v>
@@ -7831,7 +7838,7 @@
         <v>691</v>
       </c>
       <c r="D20" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E20" s="80" t="s">
         <v>692</v>
@@ -7846,7 +7853,7 @@
         <v>666</v>
       </c>
       <c r="I20" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" s="80" t="s">
         <v>693</v>
@@ -7861,7 +7868,7 @@
         <v>666</v>
       </c>
       <c r="N20" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O20" s="80" t="s">
         <v>694</v>
@@ -7876,7 +7883,7 @@
         <v>666</v>
       </c>
       <c r="S20" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T20" s="80" t="s">
         <v>695</v>
@@ -7904,7 +7911,7 @@
         <v>697</v>
       </c>
       <c r="D21" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="79" t="s">
         <v>694</v>
@@ -7919,7 +7926,7 @@
         <v>666</v>
       </c>
       <c r="I21" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="79" t="s">
         <v>667</v>
@@ -7934,7 +7941,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" s="79" t="s">
         <v>667</v>
@@ -7949,7 +7956,7 @@
         <v>666</v>
       </c>
       <c r="S21" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T21" s="79" t="s">
         <v>668</v>
@@ -7977,7 +7984,7 @@
         <v>700</v>
       </c>
       <c r="D22" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E22" s="80" t="s">
         <v>674</v>
@@ -7992,7 +7999,7 @@
         <v>666</v>
       </c>
       <c r="I22" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J22" s="80" t="s">
         <v>701</v>
@@ -8007,7 +8014,7 @@
         <v>1</v>
       </c>
       <c r="N22" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O22" s="80" t="s">
         <v>672</v>
@@ -8022,7 +8029,7 @@
         <v>1</v>
       </c>
       <c r="S22" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T22" s="80" t="s">
         <v>703</v>
@@ -8050,7 +8057,7 @@
         <v>705</v>
       </c>
       <c r="D23" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="79" t="s">
         <v>706</v>
@@ -8065,7 +8072,7 @@
         <v>666</v>
       </c>
       <c r="I23" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="79" t="s">
         <v>672</v>
@@ -8080,7 +8087,7 @@
         <v>1</v>
       </c>
       <c r="N23" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O23" s="79" t="s">
         <v>708</v>
@@ -8095,7 +8102,7 @@
         <v>65</v>
       </c>
       <c r="S23" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T23" s="79" t="s">
         <v>708</v>
@@ -8123,7 +8130,7 @@
         <v>712</v>
       </c>
       <c r="D24" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E24" s="80" t="s">
         <v>713</v>
@@ -8138,7 +8145,7 @@
         <v>666</v>
       </c>
       <c r="I24" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J24" s="80" t="s">
         <v>714</v>
@@ -8153,7 +8160,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O24" s="80" t="s">
         <v>716</v>
@@ -8168,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="S24" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T24" s="80" t="s">
         <v>717</v>
@@ -8196,7 +8203,7 @@
         <v>719</v>
       </c>
       <c r="D25" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E25" s="79" t="s">
         <v>720</v>
@@ -8211,7 +8218,7 @@
         <v>666</v>
       </c>
       <c r="I25" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J25" s="79" t="s">
         <v>720</v>
@@ -8226,7 +8233,7 @@
         <v>666</v>
       </c>
       <c r="N25" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O25" s="79" t="s">
         <v>701</v>
@@ -8241,7 +8248,7 @@
         <v>1</v>
       </c>
       <c r="S25" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T25" s="79" t="s">
         <v>694</v>
@@ -8269,7 +8276,7 @@
         <v>723</v>
       </c>
       <c r="D26" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="80" t="s">
         <v>724</v>
@@ -8284,7 +8291,7 @@
         <v>666</v>
       </c>
       <c r="I26" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J26" s="80" t="s">
         <v>725</v>
@@ -8299,7 +8306,7 @@
         <v>1</v>
       </c>
       <c r="N26" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="80" t="s">
         <v>724</v>
@@ -8314,7 +8321,7 @@
         <v>666</v>
       </c>
       <c r="S26" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T26" s="80" t="s">
         <v>726</v>
@@ -8342,7 +8349,7 @@
         <v>728</v>
       </c>
       <c r="D27" s="83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="84" t="s">
         <v>729</v>
@@ -8357,7 +8364,7 @@
         <v>666</v>
       </c>
       <c r="I27" s="83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="84" t="s">
         <v>729</v>
@@ -8372,7 +8379,7 @@
         <v>65</v>
       </c>
       <c r="N27" s="83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O27" s="84" t="s">
         <v>730</v>
@@ -8387,7 +8394,7 @@
         <v>666</v>
       </c>
       <c r="S27" s="83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T27" s="84" t="s">
         <v>729</v>
@@ -8415,7 +8422,7 @@
         <v>732</v>
       </c>
       <c r="D28" s="74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E28" s="80" t="s">
         <v>665</v>
@@ -8430,7 +8437,7 @@
         <v>666</v>
       </c>
       <c r="I28" s="74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J28" s="80" t="s">
         <v>665</v>
@@ -8445,7 +8452,7 @@
         <v>666</v>
       </c>
       <c r="N28" s="74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O28" s="80" t="s">
         <v>665</v>
@@ -8460,7 +8467,7 @@
         <v>666</v>
       </c>
       <c r="S28" s="74">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T28" s="80" t="s">
         <v>665</v>
@@ -8488,7 +8495,7 @@
         <v>734</v>
       </c>
       <c r="D29" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E29" s="79" t="s">
         <v>735</v>
@@ -8503,7 +8510,7 @@
         <v>666</v>
       </c>
       <c r="I29" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="79" t="s">
         <v>701</v>
@@ -8518,7 +8525,7 @@
         <v>1</v>
       </c>
       <c r="N29" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O29" s="79" t="s">
         <v>737</v>
@@ -8533,7 +8540,7 @@
         <v>1</v>
       </c>
       <c r="S29" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T29" s="79" t="s">
         <v>739</v>
@@ -8561,7 +8568,7 @@
         <v>741</v>
       </c>
       <c r="D30" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E30" s="80" t="s">
         <v>742</v>
@@ -8576,7 +8583,7 @@
         <v>666</v>
       </c>
       <c r="I30" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="80" t="s">
         <v>743</v>
@@ -8591,7 +8598,7 @@
         <v>1</v>
       </c>
       <c r="N30" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O30" s="80" t="s">
         <v>707</v>
@@ -8606,7 +8613,7 @@
         <v>1</v>
       </c>
       <c r="S30" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T30" s="80" t="s">
         <v>744</v>
@@ -8634,7 +8641,7 @@
         <v>746</v>
       </c>
       <c r="D31" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E31" s="79" t="s">
         <v>747</v>
@@ -8649,7 +8656,7 @@
         <v>666</v>
       </c>
       <c r="I31" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="79" t="s">
         <v>679</v>
@@ -8664,7 +8671,7 @@
         <v>1</v>
       </c>
       <c r="N31" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O31" s="79" t="s">
         <v>749</v>
@@ -8679,7 +8686,7 @@
         <v>666</v>
       </c>
       <c r="S31" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T31" s="79" t="s">
         <v>678</v>
@@ -8707,7 +8714,7 @@
         <v>751</v>
       </c>
       <c r="D32" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E32" s="80" t="s">
         <v>678</v>
@@ -8722,7 +8729,7 @@
         <v>666</v>
       </c>
       <c r="I32" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J32" s="80" t="s">
         <v>678</v>
@@ -8737,7 +8744,7 @@
         <v>666</v>
       </c>
       <c r="N32" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O32" s="80" t="s">
         <v>752</v>
@@ -8752,7 +8759,7 @@
         <v>1</v>
       </c>
       <c r="S32" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T32" s="80" t="s">
         <v>754</v>
@@ -8780,7 +8787,7 @@
         <v>756</v>
       </c>
       <c r="D33" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E33" s="79" t="s">
         <v>757</v>
@@ -8795,7 +8802,7 @@
         <v>666</v>
       </c>
       <c r="I33" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="79" t="s">
         <v>758</v>
@@ -8810,7 +8817,7 @@
         <v>666</v>
       </c>
       <c r="N33" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O33" s="79" t="s">
         <v>757</v>
@@ -8825,7 +8832,7 @@
         <v>1</v>
       </c>
       <c r="S33" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T33" s="79" t="s">
         <v>760</v>
@@ -8853,7 +8860,7 @@
         <v>762</v>
       </c>
       <c r="D34" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E34" s="80" t="s">
         <v>763</v>
@@ -8868,7 +8875,7 @@
         <v>666</v>
       </c>
       <c r="I34" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J34" s="80" t="s">
         <v>763</v>
@@ -8883,7 +8890,7 @@
         <v>1</v>
       </c>
       <c r="N34" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O34" s="80" t="s">
         <v>765</v>
@@ -8898,7 +8905,7 @@
         <v>1</v>
       </c>
       <c r="S34" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T34" s="80" t="s">
         <v>765</v>
@@ -8926,7 +8933,7 @@
         <v>767</v>
       </c>
       <c r="D35" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E35" s="79" t="s">
         <v>768</v>
@@ -8941,7 +8948,7 @@
         <v>666</v>
       </c>
       <c r="I35" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J35" s="79" t="s">
         <v>709</v>
@@ -8956,7 +8963,7 @@
         <v>1</v>
       </c>
       <c r="N35" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O35" s="79" t="s">
         <v>769</v>
@@ -8971,7 +8978,7 @@
         <v>65</v>
       </c>
       <c r="S35" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T35" s="79" t="s">
         <v>770</v>
@@ -8999,7 +9006,7 @@
         <v>772</v>
       </c>
       <c r="D36" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E36" s="80" t="s">
         <v>698</v>
@@ -9014,7 +9021,7 @@
         <v>666</v>
       </c>
       <c r="I36" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J36" s="80" t="s">
         <v>773</v>
@@ -9029,7 +9036,7 @@
         <v>666</v>
       </c>
       <c r="N36" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O36" s="80" t="s">
         <v>774</v>
@@ -9044,7 +9051,7 @@
         <v>1</v>
       </c>
       <c r="S36" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T36" s="81" t="s">
         <v>735</v>
@@ -9072,7 +9079,7 @@
         <v>777</v>
       </c>
       <c r="D37" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E37" s="79" t="s">
         <v>778</v>
@@ -9087,7 +9094,7 @@
         <v>666</v>
       </c>
       <c r="I37" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J37" s="79" t="s">
         <v>779</v>
@@ -9102,7 +9109,7 @@
         <v>1</v>
       </c>
       <c r="N37" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O37" s="79" t="s">
         <v>778</v>
@@ -9117,7 +9124,7 @@
         <v>1</v>
       </c>
       <c r="S37" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T37" s="77" t="s">
         <v>780</v>
@@ -9145,7 +9152,7 @@
         <v>782</v>
       </c>
       <c r="D38" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E38" s="80" t="s">
         <v>716</v>
@@ -9160,7 +9167,7 @@
         <v>666</v>
       </c>
       <c r="I38" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J38" s="80" t="s">
         <v>679</v>
@@ -9175,7 +9182,7 @@
         <v>666</v>
       </c>
       <c r="N38" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O38" s="80" t="s">
         <v>783</v>
@@ -9190,7 +9197,7 @@
         <v>1</v>
       </c>
       <c r="S38" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T38" s="80" t="s">
         <v>679</v>
@@ -9218,7 +9225,7 @@
         <v>785</v>
       </c>
       <c r="D39" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E39" s="79" t="s">
         <v>673</v>
@@ -9233,7 +9240,7 @@
         <v>666</v>
       </c>
       <c r="I39" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J39" s="79" t="s">
         <v>786</v>
@@ -9248,7 +9255,7 @@
         <v>1</v>
       </c>
       <c r="N39" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O39" s="79" t="s">
         <v>673</v>
@@ -9263,7 +9270,7 @@
         <v>666</v>
       </c>
       <c r="S39" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T39" s="79" t="s">
         <v>780</v>
@@ -9291,7 +9298,7 @@
         <v>789</v>
       </c>
       <c r="D40" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="80" t="s">
         <v>790</v>
@@ -9306,7 +9313,7 @@
         <v>666</v>
       </c>
       <c r="I40" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J40" s="80" t="s">
         <v>790</v>
@@ -9321,7 +9328,7 @@
         <v>1</v>
       </c>
       <c r="N40" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O40" s="80" t="s">
         <v>683</v>
@@ -9336,7 +9343,7 @@
         <v>666</v>
       </c>
       <c r="S40" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T40" s="80" t="s">
         <v>773</v>
@@ -9364,7 +9371,7 @@
         <v>792</v>
       </c>
       <c r="D41" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E41" s="79" t="s">
         <v>793</v>
@@ -9379,7 +9386,7 @@
         <v>666</v>
       </c>
       <c r="I41" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J41" s="79" t="s">
         <v>794</v>
@@ -9394,7 +9401,7 @@
         <v>666</v>
       </c>
       <c r="N41" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" s="79" t="s">
         <v>795</v>
@@ -9409,7 +9416,7 @@
         <v>666</v>
       </c>
       <c r="S41" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T41" s="79" t="s">
         <v>793</v>
@@ -9437,7 +9444,7 @@
         <v>797</v>
       </c>
       <c r="D42" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E42" s="80" t="s">
         <v>798</v>
@@ -9452,7 +9459,7 @@
         <v>666</v>
       </c>
       <c r="I42" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J42" s="80" t="s">
         <v>799</v>
@@ -9467,7 +9474,7 @@
         <v>65</v>
       </c>
       <c r="N42" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O42" s="80" t="s">
         <v>786</v>
@@ -9482,7 +9489,7 @@
         <v>666</v>
       </c>
       <c r="S42" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T42" s="80" t="s">
         <v>720</v>
@@ -9510,7 +9517,7 @@
         <v>801</v>
       </c>
       <c r="D43" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E43" s="79" t="s">
         <v>672</v>
@@ -9525,7 +9532,7 @@
         <v>666</v>
       </c>
       <c r="I43" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J43" s="79" t="s">
         <v>757</v>
@@ -9540,7 +9547,7 @@
         <v>666</v>
       </c>
       <c r="N43" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O43" s="79" t="s">
         <v>672</v>
@@ -9555,7 +9562,7 @@
         <v>1</v>
       </c>
       <c r="S43" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T43" s="79" t="s">
         <v>688</v>
@@ -9583,7 +9590,7 @@
         <v>803</v>
       </c>
       <c r="D44" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" s="80" t="s">
         <v>804</v>
@@ -9598,7 +9605,7 @@
         <v>666</v>
       </c>
       <c r="I44" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J44" s="80" t="s">
         <v>804</v>
@@ -9613,7 +9620,7 @@
         <v>65</v>
       </c>
       <c r="N44" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O44" s="80" t="s">
         <v>805</v>
@@ -9628,7 +9635,7 @@
         <v>1</v>
       </c>
       <c r="S44" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T44" s="80" t="s">
         <v>743</v>
@@ -9656,7 +9663,7 @@
         <v>807</v>
       </c>
       <c r="D45" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E45" s="79" t="s">
         <v>808</v>
@@ -9671,7 +9678,7 @@
         <v>666</v>
       </c>
       <c r="I45" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J45" s="79" t="s">
         <v>808</v>
@@ -9686,7 +9693,7 @@
         <v>1</v>
       </c>
       <c r="N45" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O45" s="79" t="s">
         <v>809</v>
@@ -9701,7 +9708,7 @@
         <v>1</v>
       </c>
       <c r="S45" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T45" s="79" t="s">
         <v>810</v>
@@ -9729,7 +9736,7 @@
         <v>812</v>
       </c>
       <c r="D46" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E46" s="80" t="s">
         <v>813</v>
@@ -9744,7 +9751,7 @@
         <v>666</v>
       </c>
       <c r="I46" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J46" s="80" t="s">
         <v>814</v>
@@ -9759,7 +9766,7 @@
         <v>666</v>
       </c>
       <c r="N46" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O46" s="80" t="s">
         <v>677</v>
@@ -9774,7 +9781,7 @@
         <v>666</v>
       </c>
       <c r="S46" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T46" s="80" t="s">
         <v>813</v>
@@ -9802,7 +9809,7 @@
         <v>816</v>
       </c>
       <c r="D47" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E47" s="79" t="s">
         <v>817</v>
@@ -9817,7 +9824,7 @@
         <v>666</v>
       </c>
       <c r="I47" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J47" s="79" t="s">
         <v>783</v>
@@ -9832,7 +9839,7 @@
         <v>666</v>
       </c>
       <c r="N47" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O47" s="79" t="s">
         <v>701</v>
@@ -9847,7 +9854,7 @@
         <v>666</v>
       </c>
       <c r="S47" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T47" s="79" t="s">
         <v>730</v>
@@ -9875,7 +9882,7 @@
         <v>819</v>
       </c>
       <c r="D48" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E48" s="80" t="s">
         <v>820</v>
@@ -9890,7 +9897,7 @@
         <v>666</v>
       </c>
       <c r="I48" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J48" s="80" t="s">
         <v>820</v>
@@ -9905,7 +9912,7 @@
         <v>65</v>
       </c>
       <c r="N48" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" s="80" t="s">
         <v>667</v>
@@ -9920,7 +9927,7 @@
         <v>666</v>
       </c>
       <c r="S48" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T48" s="80" t="s">
         <v>673</v>
@@ -9948,7 +9955,7 @@
         <v>822</v>
       </c>
       <c r="D49" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E49" s="79" t="s">
         <v>708</v>
@@ -9963,7 +9970,7 @@
         <v>666</v>
       </c>
       <c r="I49" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J49" s="79" t="s">
         <v>765</v>
@@ -9978,7 +9985,7 @@
         <v>1</v>
       </c>
       <c r="N49" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O49" s="79" t="s">
         <v>823</v>
@@ -9993,7 +10000,7 @@
         <v>666</v>
       </c>
       <c r="S49" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T49" s="79" t="s">
         <v>824</v>
@@ -10021,7 +10028,7 @@
         <v>826</v>
       </c>
       <c r="D50" s="74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E50" s="80" t="s">
         <v>827</v>
@@ -10036,7 +10043,7 @@
         <v>666</v>
       </c>
       <c r="I50" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J50" s="80" t="s">
         <v>716</v>
@@ -10051,7 +10058,7 @@
         <v>666</v>
       </c>
       <c r="N50" s="74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O50" s="80" t="s">
         <v>827</v>
@@ -10066,7 +10073,7 @@
         <v>1</v>
       </c>
       <c r="S50" s="74">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T50" s="80" t="s">
         <v>678</v>
@@ -10094,7 +10101,7 @@
         <v>829</v>
       </c>
       <c r="D51" s="65">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E51" s="79" t="s">
         <v>725</v>
@@ -10109,7 +10116,7 @@
         <v>666</v>
       </c>
       <c r="I51" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J51" s="79" t="s">
         <v>725</v>
@@ -10124,7 +10131,7 @@
         <v>666</v>
       </c>
       <c r="N51" s="65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" s="79" t="s">
         <v>717</v>
@@ -10139,7 +10146,7 @@
         <v>666</v>
       </c>
       <c r="S51" s="65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="T51" s="79" t="s">
         <v>830</v>
@@ -10190,7 +10197,7 @@
         <v>833</v>
       </c>
       <c r="D53" s="65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E53" s="79" t="s">
         <v>665</v>
@@ -10205,7 +10212,7 @@
         <v>666</v>
       </c>
       <c r="I53" s="65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J53" s="79" t="s">
         <v>665</v>
@@ -10220,7 +10227,7 @@
         <v>666</v>
       </c>
       <c r="N53" s="65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O53" s="79" t="s">
         <v>665</v>
@@ -10235,7 +10242,7 @@
         <v>666</v>
       </c>
       <c r="S53" s="65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T53" s="79" t="s">
         <v>665</v>

--- a/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -58,7 +58,7 @@
       </rPr>
       <t xml:space="preserve">
 作者：整洁的魔理沙
-文档版本：V2.5.26.580
+文档版本：V2.5.26.605
 七日杀游戏版本：V2.5</t>
     </r>
   </si>
@@ -3608,8 +3608,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <color rgb="FFF09457"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -3622,8 +3622,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFF09457"/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>

--- a/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29700" windowHeight="16840" activeTab="9"/>
+    <workbookView windowWidth="29700" windowHeight="16840"/>
   </bookViews>
   <sheets>
     <sheet name="首页" sheetId="15" r:id="rId1"/>
@@ -46,13 +46,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="1115">
   <si>
     <r>
-      <rPr>
-        <sz val="48"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">虹彩炼金3-战痕
 </t>
     </r>
@@ -66,7 +59,7 @@
       </rPr>
       <t xml:space="preserve">
 作者：整洁的魔理沙
-文档版本：V2.5.26.615
+文档版本：V2.5.26.636
 七日杀游戏版本：V2.5</t>
     </r>
   </si>
@@ -3742,6 +3735,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="24"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -3751,13 +3751,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFF09457"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>

--- a/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29700" windowHeight="16840"/>
+    <workbookView windowWidth="29700" windowHeight="16840" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="首页" sheetId="15" r:id="rId1"/>
@@ -46,6 +46,13 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3591" uniqueCount="1115">
   <si>
     <r>
+      <rPr>
+        <sz val="48"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">虹彩炼金3-战痕
 </t>
     </r>
@@ -9112,7 +9119,7 @@
     </row>
     <row r="80" spans="2:17">
       <c r="B80" s="150" t="s">
-        <v>211</v>
+        <v>547</v>
       </c>
       <c r="C80" s="150" t="s">
         <v>625</v>

--- a/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
+++ b/IridescentAlchemy3-TraceOfBattle/ReadMe.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29700" windowHeight="16840" activeTab="9"/>
+    <workbookView windowWidth="29700" windowHeight="16840" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="首页" sheetId="15" r:id="rId1"/>
@@ -2902,7 +2902,7 @@
     <t>狂化30</t>
   </si>
   <si>
-    <t>3件套</t>
+    <t>2件套</t>
   </si>
   <si>
     <t>【极意】潜伏</t>
@@ -3742,15 +3742,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
+      <sz val="24"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="24"/>
-      <color theme="1"/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
